--- a/Team-Data/2008-09/3-7-2008-09.xlsx
+++ b/Team-Data/2008-09/3-7-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E2" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F2" t="n">
         <v>28</v>
       </c>
       <c r="G2" t="n">
-        <v>0.556</v>
+        <v>0.548</v>
       </c>
       <c r="H2" t="n">
         <v>48.1</v>
@@ -682,28 +749,28 @@
         <v>78.7</v>
       </c>
       <c r="K2" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="L2" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="M2" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="N2" t="n">
-        <v>0.362</v>
+        <v>0.363</v>
       </c>
       <c r="O2" t="n">
         <v>18.9</v>
       </c>
       <c r="P2" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.736</v>
+        <v>0.735</v>
       </c>
       <c r="R2" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="S2" t="n">
         <v>29.3</v>
@@ -715,7 +782,7 @@
         <v>20.5</v>
       </c>
       <c r="V2" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="W2" t="n">
         <v>7.4</v>
@@ -733,13 +800,13 @@
         <v>20.7</v>
       </c>
       <c r="AB2" t="n">
-        <v>98.2</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AD2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AE2" t="n">
         <v>12</v>
@@ -754,13 +821,13 @@
         <v>29</v>
       </c>
       <c r="AI2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AJ2" t="n">
         <v>23</v>
       </c>
       <c r="AK2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AL2" t="n">
         <v>9</v>
@@ -769,7 +836,7 @@
         <v>7</v>
       </c>
       <c r="AN2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO2" t="n">
         <v>18</v>
@@ -796,10 +863,10 @@
         <v>6</v>
       </c>
       <c r="AW2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-7-2008-09</t>
+          <t>2009-03-07</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F3" t="n">
         <v>14</v>
       </c>
       <c r="G3" t="n">
-        <v>0.774</v>
+        <v>0.778</v>
       </c>
       <c r="H3" t="n">
         <v>48.4</v>
@@ -864,67 +931,67 @@
         <v>77</v>
       </c>
       <c r="K3" t="n">
-        <v>0.489</v>
+        <v>0.488</v>
       </c>
       <c r="L3" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M3" t="n">
         <v>16.6</v>
       </c>
       <c r="N3" t="n">
-        <v>0.394</v>
+        <v>0.392</v>
       </c>
       <c r="O3" t="n">
         <v>20.1</v>
       </c>
       <c r="P3" t="n">
-        <v>25.9</v>
+        <v>26.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.775</v>
+        <v>0.772</v>
       </c>
       <c r="R3" t="n">
         <v>10.7</v>
       </c>
       <c r="S3" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="T3" t="n">
-        <v>42.5</v>
+        <v>42.4</v>
       </c>
       <c r="U3" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="V3" t="n">
         <v>15.8</v>
       </c>
       <c r="W3" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="X3" t="n">
         <v>4.7</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.9</v>
+        <v>101.7</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AE3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF3" t="n">
         <v>3</v>
@@ -933,10 +1000,10 @@
         <v>3</v>
       </c>
       <c r="AH3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AI3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ3" t="n">
         <v>28</v>
@@ -957,19 +1024,19 @@
         <v>9</v>
       </c>
       <c r="AP3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AR3" t="n">
         <v>20</v>
       </c>
       <c r="AS3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AU3" t="n">
         <v>3</v>
@@ -981,16 +1048,16 @@
         <v>7</v>
       </c>
       <c r="AX3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ3" t="n">
         <v>27</v>
       </c>
       <c r="BA3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB3" t="n">
         <v>9</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-7-2008-09</t>
+          <t>2009-03-07</t>
         </is>
       </c>
     </row>
@@ -1025,52 +1092,52 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F4" t="n">
         <v>35</v>
       </c>
       <c r="G4" t="n">
-        <v>0.444</v>
+        <v>0.435</v>
       </c>
       <c r="H4" t="n">
         <v>48.6</v>
       </c>
       <c r="I4" t="n">
-        <v>34.7</v>
+        <v>34.6</v>
       </c>
       <c r="J4" t="n">
         <v>76.59999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.454</v>
+        <v>0.452</v>
       </c>
       <c r="L4" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="M4" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="N4" t="n">
-        <v>0.374</v>
+        <v>0.371</v>
       </c>
       <c r="O4" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="P4" t="n">
         <v>23.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.743</v>
+        <v>0.74</v>
       </c>
       <c r="R4" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="S4" t="n">
-        <v>28.8</v>
+        <v>28.7</v>
       </c>
       <c r="T4" t="n">
         <v>39.5</v>
@@ -1079,7 +1146,7 @@
         <v>21.2</v>
       </c>
       <c r="V4" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="W4" t="n">
         <v>7</v>
@@ -1088,7 +1155,7 @@
         <v>4.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="Z4" t="n">
         <v>22</v>
@@ -1097,16 +1164,16 @@
         <v>21</v>
       </c>
       <c r="AB4" t="n">
-        <v>93.3</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1.3</v>
+        <v>-1.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AE4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF4" t="n">
         <v>18</v>
@@ -1124,16 +1191,16 @@
         <v>30</v>
       </c>
       <c r="AK4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM4" t="n">
         <v>23</v>
       </c>
       <c r="AN4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AO4" t="n">
         <v>25</v>
@@ -1142,13 +1209,13 @@
         <v>20</v>
       </c>
       <c r="AQ4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AR4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AS4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AT4" t="n">
         <v>26</v>
@@ -1160,7 +1227,7 @@
         <v>25</v>
       </c>
       <c r="AW4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX4" t="n">
         <v>14</v>
@@ -1172,13 +1239,13 @@
         <v>20</v>
       </c>
       <c r="BA4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB4" t="n">
         <v>30</v>
       </c>
       <c r="BC4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-7-2008-09</t>
+          <t>2009-03-07</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F5" t="n">
         <v>34</v>
       </c>
       <c r="G5" t="n">
-        <v>0.452</v>
+        <v>0.46</v>
       </c>
       <c r="H5" t="n">
         <v>48.6</v>
@@ -1225,10 +1292,10 @@
         <v>37.6</v>
       </c>
       <c r="J5" t="n">
-        <v>83.5</v>
+        <v>83.2</v>
       </c>
       <c r="K5" t="n">
-        <v>0.451</v>
+        <v>0.452</v>
       </c>
       <c r="L5" t="n">
         <v>5.8</v>
@@ -1237,67 +1304,67 @@
         <v>15.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0.376</v>
+        <v>0.377</v>
       </c>
       <c r="O5" t="n">
-        <v>19.7</v>
+        <v>19.9</v>
       </c>
       <c r="P5" t="n">
-        <v>24.9</v>
+        <v>25.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.791</v>
+        <v>0.79</v>
       </c>
       <c r="R5" t="n">
         <v>12.1</v>
       </c>
       <c r="S5" t="n">
-        <v>30.5</v>
+        <v>30.4</v>
       </c>
       <c r="T5" t="n">
         <v>42.6</v>
       </c>
       <c r="U5" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="V5" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W5" t="n">
         <v>7.5</v>
       </c>
       <c r="X5" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Z5" t="n">
         <v>21.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="AB5" t="n">
-        <v>100.8</v>
+        <v>100.9</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1.3</v>
+        <v>-1.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AE5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AF5" t="n">
         <v>17</v>
       </c>
       <c r="AG5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AI5" t="n">
         <v>8</v>
@@ -1306,7 +1373,7 @@
         <v>6</v>
       </c>
       <c r="AK5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AL5" t="n">
         <v>24</v>
@@ -1315,7 +1382,7 @@
         <v>24</v>
       </c>
       <c r="AN5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO5" t="n">
         <v>11</v>
@@ -1333,13 +1400,13 @@
         <v>12</v>
       </c>
       <c r="AT5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW5" t="n">
         <v>10</v>
@@ -1354,13 +1421,13 @@
         <v>19</v>
       </c>
       <c r="BA5" t="n">
+        <v>17</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC5" t="n">
         <v>18</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>11</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>19</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-7-2008-09</t>
+          <t>2009-03-07</t>
         </is>
       </c>
     </row>
@@ -1392,40 +1459,40 @@
         <v>61</v>
       </c>
       <c r="E6" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6" t="n">
-        <v>0.803</v>
+        <v>0.787</v>
       </c>
       <c r="H6" t="n">
         <v>48.1</v>
       </c>
       <c r="I6" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="J6" t="n">
-        <v>78</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.47</v>
+        <v>0.469</v>
       </c>
       <c r="L6" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="M6" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0.395</v>
+        <v>0.39</v>
       </c>
       <c r="O6" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="P6" t="n">
-        <v>24.8</v>
+        <v>25</v>
       </c>
       <c r="Q6" t="n">
         <v>0.754</v>
@@ -1440,46 +1507,46 @@
         <v>41.6</v>
       </c>
       <c r="U6" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="V6" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="W6" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="X6" t="n">
         <v>5.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.1</v>
+        <v>20.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>100.1</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AD6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AE6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI6" t="n">
         <v>17</v>
@@ -1497,7 +1564,7 @@
         <v>6</v>
       </c>
       <c r="AN6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AO6" t="n">
         <v>19</v>
@@ -1506,7 +1573,7 @@
         <v>15</v>
       </c>
       <c r="AQ6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR6" t="n">
         <v>19</v>
@@ -1521,7 +1588,7 @@
         <v>25</v>
       </c>
       <c r="AV6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW6" t="n">
         <v>8</v>
@@ -1530,10 +1597,10 @@
         <v>6</v>
       </c>
       <c r="AY6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>7</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>6</v>
       </c>
       <c r="BA6" t="n">
         <v>21</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-7-2008-09</t>
+          <t>2009-03-07</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E7" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F7" t="n">
         <v>25</v>
       </c>
       <c r="G7" t="n">
-        <v>0.603</v>
+        <v>0.597</v>
       </c>
       <c r="H7" t="n">
         <v>48.4</v>
@@ -1592,43 +1659,43 @@
         <v>82.7</v>
       </c>
       <c r="K7" t="n">
-        <v>0.46</v>
+        <v>0.459</v>
       </c>
       <c r="L7" t="n">
         <v>6.7</v>
       </c>
       <c r="M7" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="N7" t="n">
-        <v>0.347</v>
+        <v>0.345</v>
       </c>
       <c r="O7" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="P7" t="n">
-        <v>22.3</v>
+        <v>22.1</v>
       </c>
       <c r="Q7" t="n">
         <v>0.82</v>
       </c>
       <c r="R7" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="S7" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="T7" t="n">
-        <v>42.8</v>
+        <v>42.9</v>
       </c>
       <c r="U7" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="V7" t="n">
         <v>13.3</v>
       </c>
       <c r="W7" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X7" t="n">
         <v>5.4</v>
@@ -1637,19 +1704,19 @@
         <v>4.1</v>
       </c>
       <c r="Z7" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="AA7" t="n">
         <v>20</v>
       </c>
       <c r="AB7" t="n">
-        <v>101.1</v>
+        <v>100.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AE7" t="n">
         <v>11</v>
@@ -1661,7 +1728,7 @@
         <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI7" t="n">
         <v>7</v>
@@ -1670,7 +1737,7 @@
         <v>7</v>
       </c>
       <c r="AK7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL7" t="n">
         <v>13</v>
@@ -1697,22 +1764,22 @@
         <v>7</v>
       </c>
       <c r="AT7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AU7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV7" t="n">
         <v>10</v>
       </c>
       <c r="AW7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX7" t="n">
         <v>7</v>
       </c>
       <c r="AY7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ7" t="n">
         <v>3</v>
@@ -1721,7 +1788,7 @@
         <v>24</v>
       </c>
       <c r="BB7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC7" t="n">
         <v>12</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-7-2008-09</t>
+          <t>2009-03-07</t>
         </is>
       </c>
     </row>
@@ -1837,16 +1904,16 @@
         <v>6</v>
       </c>
       <c r="AF8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AH8" t="n">
         <v>25</v>
       </c>
       <c r="AI8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ8" t="n">
         <v>24</v>
@@ -1861,7 +1928,7 @@
         <v>18</v>
       </c>
       <c r="AN8" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1873,13 +1940,13 @@
         <v>22</v>
       </c>
       <c r="AR8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS8" t="n">
         <v>13</v>
       </c>
       <c r="AT8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AU8" t="n">
         <v>6</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-7-2008-09</t>
+          <t>2009-03-07</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E9" t="n">
         <v>31</v>
       </c>
       <c r="F9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G9" t="n">
-        <v>0.508</v>
+        <v>0.517</v>
       </c>
       <c r="H9" t="n">
         <v>48.3</v>
@@ -1962,22 +2029,22 @@
         <v>4.6</v>
       </c>
       <c r="M9" t="n">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="N9" t="n">
-        <v>0.343</v>
+        <v>0.345</v>
       </c>
       <c r="O9" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="P9" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.752</v>
+        <v>0.751</v>
       </c>
       <c r="R9" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="S9" t="n">
         <v>29.8</v>
@@ -1986,13 +2053,13 @@
         <v>40.7</v>
       </c>
       <c r="U9" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="V9" t="n">
         <v>11.9</v>
       </c>
       <c r="W9" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="X9" t="n">
         <v>4.7</v>
@@ -2004,16 +2071,16 @@
         <v>21</v>
       </c>
       <c r="AA9" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AB9" t="n">
-        <v>93.40000000000001</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AC9" t="n">
         <v>-0.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AE9" t="n">
         <v>15</v>
@@ -2034,7 +2101,7 @@
         <v>22</v>
       </c>
       <c r="AK9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL9" t="n">
         <v>28</v>
@@ -2049,7 +2116,7 @@
         <v>27</v>
       </c>
       <c r="AP9" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AQ9" t="n">
         <v>25</v>
@@ -2058,7 +2125,7 @@
         <v>15</v>
       </c>
       <c r="AS9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AT9" t="n">
         <v>20</v>
@@ -2073,10 +2140,10 @@
         <v>28</v>
       </c>
       <c r="AX9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ9" t="n">
         <v>18</v>
@@ -2088,7 +2155,7 @@
         <v>29</v>
       </c>
       <c r="BC9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-7-2008-09</t>
+          <t>2009-03-07</t>
         </is>
       </c>
     </row>
@@ -2117,49 +2184,49 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E10" t="n">
         <v>21</v>
       </c>
       <c r="F10" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G10" t="n">
-        <v>0.333</v>
+        <v>0.339</v>
       </c>
       <c r="H10" t="n">
         <v>48.6</v>
       </c>
       <c r="I10" t="n">
-        <v>39.2</v>
+        <v>39.1</v>
       </c>
       <c r="J10" t="n">
-        <v>85.59999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="K10" t="n">
         <v>0.457</v>
       </c>
       <c r="L10" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="M10" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="N10" t="n">
         <v>0.373</v>
       </c>
       <c r="O10" t="n">
-        <v>22.9</v>
+        <v>22.7</v>
       </c>
       <c r="P10" t="n">
-        <v>29.2</v>
+        <v>29</v>
       </c>
       <c r="Q10" t="n">
         <v>0.783</v>
       </c>
       <c r="R10" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="S10" t="n">
         <v>30.1</v>
@@ -2168,34 +2235,34 @@
         <v>41.7</v>
       </c>
       <c r="U10" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="V10" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W10" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="X10" t="n">
         <v>6.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z10" t="n">
         <v>22.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>107.8</v>
+        <v>107.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>-3.7</v>
+        <v>-3.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AE10" t="n">
         <v>24</v>
@@ -2207,7 +2274,7 @@
         <v>24</v>
       </c>
       <c r="AH10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI10" t="n">
         <v>3</v>
@@ -2216,25 +2283,25 @@
         <v>3</v>
       </c>
       <c r="AK10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AL10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AM10" t="n">
         <v>17</v>
       </c>
       <c r="AN10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP10" t="n">
         <v>2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR10" t="n">
         <v>10</v>
@@ -2249,10 +2316,10 @@
         <v>15</v>
       </c>
       <c r="AV10" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AW10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AX10" t="n">
         <v>1</v>
@@ -2270,7 +2337,7 @@
         <v>2</v>
       </c>
       <c r="BC10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-7-2008-09</t>
+          <t>2009-03-07</t>
         </is>
       </c>
     </row>
@@ -2383,22 +2450,22 @@
         <v>6</v>
       </c>
       <c r="AF11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AH11" t="n">
         <v>21</v>
       </c>
       <c r="AI11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ11" t="n">
         <v>20</v>
       </c>
       <c r="AK11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL11" t="n">
         <v>7</v>
@@ -2407,7 +2474,7 @@
         <v>5</v>
       </c>
       <c r="AN11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO11" t="n">
         <v>12</v>
@@ -2425,13 +2492,13 @@
         <v>2</v>
       </c>
       <c r="AT11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AU11" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AV11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW11" t="n">
         <v>25</v>
@@ -2446,13 +2513,13 @@
         <v>1</v>
       </c>
       <c r="BA11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB11" t="n">
         <v>16</v>
       </c>
       <c r="BC11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-7-2008-09</t>
+          <t>2009-03-07</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F12" t="n">
         <v>37</v>
       </c>
       <c r="G12" t="n">
-        <v>0.431</v>
+        <v>0.422</v>
       </c>
       <c r="H12" t="n">
         <v>48.5</v>
@@ -2502,7 +2569,7 @@
         <v>86.3</v>
       </c>
       <c r="K12" t="n">
-        <v>0.452</v>
+        <v>0.451</v>
       </c>
       <c r="L12" t="n">
         <v>7.9</v>
@@ -2514,13 +2581,13 @@
         <v>0.376</v>
       </c>
       <c r="O12" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="P12" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.806</v>
+        <v>0.805</v>
       </c>
       <c r="R12" t="n">
         <v>11.4</v>
@@ -2529,16 +2596,16 @@
         <v>32.2</v>
       </c>
       <c r="T12" t="n">
-        <v>43.6</v>
+        <v>43.7</v>
       </c>
       <c r="U12" t="n">
         <v>22.2</v>
       </c>
       <c r="V12" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W12" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X12" t="n">
         <v>5.2</v>
@@ -2559,10 +2626,10 @@
         <v>-1.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF12" t="n">
         <v>22</v>
@@ -2580,7 +2647,7 @@
         <v>2</v>
       </c>
       <c r="AK12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL12" t="n">
         <v>4</v>
@@ -2598,7 +2665,7 @@
         <v>21</v>
       </c>
       <c r="AQ12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AR12" t="n">
         <v>11</v>
@@ -2613,10 +2680,10 @@
         <v>5</v>
       </c>
       <c r="AV12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX12" t="n">
         <v>11</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-7-2008-09</t>
+          <t>2009-03-07</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E13" t="n">
         <v>15</v>
       </c>
       <c r="F13" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G13" t="n">
-        <v>0.238</v>
+        <v>0.242</v>
       </c>
       <c r="H13" t="n">
         <v>48.6</v>
@@ -2684,16 +2751,16 @@
         <v>82</v>
       </c>
       <c r="K13" t="n">
-        <v>0.437</v>
+        <v>0.436</v>
       </c>
       <c r="L13" t="n">
         <v>6.4</v>
       </c>
       <c r="M13" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="N13" t="n">
-        <v>0.349</v>
+        <v>0.347</v>
       </c>
       <c r="O13" t="n">
         <v>16.9</v>
@@ -2702,7 +2769,7 @@
         <v>22.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.741</v>
+        <v>0.742</v>
       </c>
       <c r="R13" t="n">
         <v>11.2</v>
@@ -2711,13 +2778,13 @@
         <v>28.9</v>
       </c>
       <c r="T13" t="n">
-        <v>40.2</v>
+        <v>40.1</v>
       </c>
       <c r="U13" t="n">
         <v>21</v>
       </c>
       <c r="V13" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="W13" t="n">
         <v>7</v>
@@ -2735,13 +2802,13 @@
         <v>19.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>95</v>
+        <v>94.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>-8.699999999999999</v>
+        <v>-8.9</v>
       </c>
       <c r="AD13" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AE13" t="n">
         <v>28</v>
@@ -2753,10 +2820,10 @@
         <v>28</v>
       </c>
       <c r="AH13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AI13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ13" t="n">
         <v>8</v>
@@ -2768,19 +2835,19 @@
         <v>18</v>
       </c>
       <c r="AM13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AN13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AP13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AR13" t="n">
         <v>12</v>
@@ -2789,16 +2856,16 @@
         <v>25</v>
       </c>
       <c r="AT13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV13" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW13" t="n">
         <v>20</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>23</v>
       </c>
       <c r="AX13" t="n">
         <v>2</v>
@@ -2807,7 +2874,7 @@
         <v>21</v>
       </c>
       <c r="AZ13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA13" t="n">
         <v>26</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-7-2008-09</t>
+          <t>2009-03-07</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E14" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F14" t="n">
         <v>12</v>
       </c>
       <c r="G14" t="n">
-        <v>0.803</v>
+        <v>0.806</v>
       </c>
       <c r="H14" t="n">
         <v>48.3</v>
@@ -2863,7 +2930,7 @@
         <v>40.7</v>
       </c>
       <c r="J14" t="n">
-        <v>85.59999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="K14" t="n">
         <v>0.476</v>
@@ -2872,28 +2939,28 @@
         <v>6.9</v>
       </c>
       <c r="M14" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="N14" t="n">
-        <v>0.362</v>
+        <v>0.365</v>
       </c>
       <c r="O14" t="n">
         <v>20.5</v>
       </c>
       <c r="P14" t="n">
-        <v>26.7</v>
+        <v>26.5</v>
       </c>
       <c r="Q14" t="n">
         <v>0.77</v>
       </c>
       <c r="R14" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="S14" t="n">
-        <v>31.7</v>
+        <v>31.9</v>
       </c>
       <c r="T14" t="n">
-        <v>44.4</v>
+        <v>44.5</v>
       </c>
       <c r="U14" t="n">
         <v>23.7</v>
@@ -2902,28 +2969,28 @@
         <v>13.5</v>
       </c>
       <c r="W14" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="X14" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Y14" t="n">
         <v>4.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="AB14" t="n">
-        <v>108.9</v>
+        <v>108.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2935,7 +3002,7 @@
         <v>1</v>
       </c>
       <c r="AH14" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AI14" t="n">
         <v>1</v>
@@ -2950,7 +3017,7 @@
         <v>12</v>
       </c>
       <c r="AM14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AN14" t="n">
         <v>17</v>
@@ -2962,13 +3029,13 @@
         <v>6</v>
       </c>
       <c r="AQ14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR14" t="n">
         <v>3</v>
       </c>
       <c r="AS14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT14" t="n">
         <v>1</v>
@@ -2989,10 +3056,10 @@
         <v>13</v>
       </c>
       <c r="AZ14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-7-2008-09</t>
+          <t>2009-03-07</t>
         </is>
       </c>
     </row>
@@ -3027,46 +3094,46 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E15" t="n">
         <v>16</v>
       </c>
       <c r="F15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G15" t="n">
-        <v>0.262</v>
+        <v>0.267</v>
       </c>
       <c r="H15" t="n">
         <v>48.4</v>
       </c>
       <c r="I15" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="J15" t="n">
         <v>77.5</v>
       </c>
       <c r="K15" t="n">
-        <v>0.452</v>
+        <v>0.45</v>
       </c>
       <c r="L15" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="M15" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="N15" t="n">
         <v>0.339</v>
       </c>
       <c r="O15" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="P15" t="n">
-        <v>25.4</v>
+        <v>25.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.753</v>
+        <v>0.754</v>
       </c>
       <c r="R15" t="n">
         <v>10.6</v>
@@ -3078,13 +3145,13 @@
         <v>39.3</v>
       </c>
       <c r="U15" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="V15" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="W15" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X15" t="n">
         <v>4.5</v>
@@ -3099,13 +3166,13 @@
         <v>21.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>93.8</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AC15" t="n">
         <v>-6</v>
       </c>
       <c r="AD15" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AE15" t="n">
         <v>26</v>
@@ -3126,7 +3193,7 @@
         <v>27</v>
       </c>
       <c r="AK15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AL15" t="n">
         <v>27</v>
@@ -3144,7 +3211,7 @@
         <v>13</v>
       </c>
       <c r="AQ15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR15" t="n">
         <v>21</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-7-2008-09</t>
+          <t>2009-03-07</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E16" t="n">
         <v>33</v>
       </c>
       <c r="F16" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G16" t="n">
-        <v>0.532</v>
+        <v>0.541</v>
       </c>
       <c r="H16" t="n">
         <v>48.2</v>
@@ -3233,28 +3300,28 @@
         <v>0.455</v>
       </c>
       <c r="L16" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="M16" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="N16" t="n">
-        <v>0.352</v>
+        <v>0.354</v>
       </c>
       <c r="O16" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="P16" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.758</v>
+        <v>0.756</v>
       </c>
       <c r="R16" t="n">
         <v>10.2</v>
       </c>
       <c r="S16" t="n">
-        <v>29.1</v>
+        <v>29</v>
       </c>
       <c r="T16" t="n">
         <v>39.2</v>
@@ -3278,22 +3345,22 @@
         <v>20.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AB16" t="n">
-        <v>97.5</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AE16" t="n">
         <v>14</v>
       </c>
       <c r="AF16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AG16" t="n">
         <v>14</v>
@@ -3308,7 +3375,7 @@
         <v>11</v>
       </c>
       <c r="AK16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL16" t="n">
         <v>11</v>
@@ -3320,13 +3387,13 @@
         <v>22</v>
       </c>
       <c r="AO16" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP16" t="n">
         <v>28</v>
       </c>
       <c r="AQ16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR16" t="n">
         <v>25</v>
@@ -3341,25 +3408,25 @@
         <v>23</v>
       </c>
       <c r="AV16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX16" t="n">
         <v>5</v>
       </c>
       <c r="AY16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC16" t="n">
         <v>15</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-7-2008-09</t>
+          <t>2009-03-07</t>
         </is>
       </c>
     </row>
@@ -3394,22 +3461,22 @@
         <v>65</v>
       </c>
       <c r="E17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G17" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H17" t="n">
         <v>48.3</v>
       </c>
       <c r="I17" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="J17" t="n">
-        <v>82</v>
+        <v>81.7</v>
       </c>
       <c r="K17" t="n">
         <v>0.448</v>
@@ -3421,52 +3488,52 @@
         <v>16.6</v>
       </c>
       <c r="N17" t="n">
-        <v>0.362</v>
+        <v>0.36</v>
       </c>
       <c r="O17" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="P17" t="n">
-        <v>26</v>
+        <v>25.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.783</v>
+        <v>0.781</v>
       </c>
       <c r="R17" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="S17" t="n">
-        <v>29.1</v>
+        <v>29</v>
       </c>
       <c r="T17" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="U17" t="n">
         <v>21.6</v>
       </c>
       <c r="V17" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W17" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="X17" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Y17" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z17" t="n">
         <v>24.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>99.8</v>
+        <v>99.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.2</v>
+        <v>-0.6</v>
       </c>
       <c r="AD17" t="n">
         <v>1</v>
@@ -3475,10 +3542,10 @@
         <v>16</v>
       </c>
       <c r="AF17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG17" t="n">
         <v>18</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>17</v>
       </c>
       <c r="AH17" t="n">
         <v>18</v>
@@ -3487,28 +3554,28 @@
         <v>16</v>
       </c>
       <c r="AJ17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK17" t="n">
         <v>24</v>
       </c>
       <c r="AL17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AM17" t="n">
         <v>21</v>
       </c>
       <c r="AN17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AQ17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR17" t="n">
         <v>6</v>
@@ -3517,16 +3584,16 @@
         <v>24</v>
       </c>
       <c r="AT17" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AU17" t="n">
         <v>9</v>
       </c>
       <c r="AV17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX17" t="n">
         <v>29</v>
@@ -3544,7 +3611,7 @@
         <v>13</v>
       </c>
       <c r="BC17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-7-2008-09</t>
+          <t>2009-03-07</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E18" t="n">
         <v>18</v>
       </c>
       <c r="F18" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G18" t="n">
-        <v>0.29</v>
+        <v>0.295</v>
       </c>
       <c r="H18" t="n">
         <v>48.4</v>
@@ -3591,7 +3658,7 @@
         <v>36.8</v>
       </c>
       <c r="J18" t="n">
-        <v>83.5</v>
+        <v>83.7</v>
       </c>
       <c r="K18" t="n">
         <v>0.44</v>
@@ -3600,34 +3667,34 @@
         <v>6.2</v>
       </c>
       <c r="M18" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="N18" t="n">
         <v>0.342</v>
       </c>
       <c r="O18" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="P18" t="n">
-        <v>24.6</v>
+        <v>24.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.772</v>
+        <v>0.77</v>
       </c>
       <c r="R18" t="n">
         <v>12.3</v>
       </c>
       <c r="S18" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="T18" t="n">
-        <v>42</v>
+        <v>42.1</v>
       </c>
       <c r="U18" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="V18" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W18" t="n">
         <v>6.5</v>
@@ -3639,19 +3706,19 @@
         <v>6.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="AA18" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>98.8</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="AC18" t="n">
-        <v>-4.9</v>
+        <v>-5</v>
       </c>
       <c r="AD18" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AE18" t="n">
         <v>25</v>
@@ -3666,7 +3733,7 @@
         <v>10</v>
       </c>
       <c r="AI18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ18" t="n">
         <v>5</v>
@@ -3690,28 +3757,28 @@
         <v>16</v>
       </c>
       <c r="AQ18" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AR18" t="n">
         <v>5</v>
       </c>
       <c r="AS18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT18" t="n">
         <v>11</v>
       </c>
       <c r="AU18" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AV18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW18" t="n">
         <v>27</v>
       </c>
       <c r="AX18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY18" t="n">
         <v>30</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-7-2008-09</t>
+          <t>2009-03-07</t>
         </is>
       </c>
     </row>
@@ -3833,16 +3900,16 @@
         <v>-2.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AE19" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AF19" t="n">
         <v>18</v>
       </c>
       <c r="AG19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH19" t="n">
         <v>7</v>
@@ -3863,7 +3930,7 @@
         <v>4</v>
       </c>
       <c r="AN19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO19" t="n">
         <v>14</v>
@@ -3875,13 +3942,13 @@
         <v>9</v>
       </c>
       <c r="AR19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS19" t="n">
         <v>20</v>
       </c>
       <c r="AT19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU19" t="n">
         <v>28</v>
@@ -3890,19 +3957,19 @@
         <v>9</v>
       </c>
       <c r="AW19" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AX19" t="n">
         <v>20</v>
       </c>
       <c r="AY19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ19" t="n">
         <v>25</v>
       </c>
       <c r="BA19" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BB19" t="n">
         <v>18</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-7-2008-09</t>
+          <t>2009-03-07</t>
         </is>
       </c>
     </row>
@@ -3937,28 +4004,28 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E20" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F20" t="n">
         <v>22</v>
       </c>
       <c r="G20" t="n">
-        <v>0.639</v>
+        <v>0.633</v>
       </c>
       <c r="H20" t="n">
         <v>48.1</v>
       </c>
       <c r="I20" t="n">
-        <v>35.2</v>
+        <v>35.1</v>
       </c>
       <c r="J20" t="n">
-        <v>77</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="L20" t="n">
         <v>7.5</v>
@@ -3967,7 +4034,7 @@
         <v>19.7</v>
       </c>
       <c r="N20" t="n">
-        <v>0.379</v>
+        <v>0.38</v>
       </c>
       <c r="O20" t="n">
         <v>18.6</v>
@@ -3976,19 +4043,19 @@
         <v>23.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.805</v>
+        <v>0.806</v>
       </c>
       <c r="R20" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="S20" t="n">
-        <v>30</v>
+        <v>29.9</v>
       </c>
       <c r="T20" t="n">
-        <v>39.7</v>
+        <v>39.6</v>
       </c>
       <c r="U20" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="V20" t="n">
         <v>12.6</v>
@@ -3997,37 +4064,37 @@
         <v>7.3</v>
       </c>
       <c r="X20" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Y20" t="n">
         <v>3.6</v>
       </c>
       <c r="Z20" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AA20" t="n">
         <v>21</v>
       </c>
       <c r="AB20" t="n">
-        <v>96.5</v>
+        <v>96.3</v>
       </c>
       <c r="AC20" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AE20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF20" t="n">
         <v>6</v>
       </c>
       <c r="AG20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AH20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI20" t="n">
         <v>28</v>
@@ -4036,7 +4103,7 @@
         <v>29</v>
       </c>
       <c r="AK20" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AL20" t="n">
         <v>8</v>
@@ -4045,16 +4112,16 @@
         <v>9</v>
       </c>
       <c r="AN20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP20" t="n">
         <v>22</v>
       </c>
       <c r="AQ20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR20" t="n">
         <v>28</v>
@@ -4063,16 +4130,16 @@
         <v>16</v>
       </c>
       <c r="AT20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU20" t="n">
         <v>26</v>
       </c>
       <c r="AV20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW20" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AX20" t="n">
         <v>24</v>
@@ -4081,7 +4148,7 @@
         <v>1</v>
       </c>
       <c r="AZ20" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BA20" t="n">
         <v>14</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-7-2008-09</t>
+          <t>2009-03-07</t>
         </is>
       </c>
     </row>
@@ -4119,25 +4186,25 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E21" t="n">
         <v>25</v>
       </c>
       <c r="F21" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G21" t="n">
-        <v>0.41</v>
+        <v>0.417</v>
       </c>
       <c r="H21" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="I21" t="n">
-        <v>38.6</v>
+        <v>38.7</v>
       </c>
       <c r="J21" t="n">
-        <v>86.8</v>
+        <v>87</v>
       </c>
       <c r="K21" t="n">
         <v>0.445</v>
@@ -4149,13 +4216,13 @@
         <v>28.8</v>
       </c>
       <c r="N21" t="n">
-        <v>0.365</v>
+        <v>0.366</v>
       </c>
       <c r="O21" t="n">
-        <v>18.3</v>
+        <v>18.1</v>
       </c>
       <c r="P21" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="Q21" t="n">
         <v>0.794</v>
@@ -4164,13 +4231,13 @@
         <v>11.1</v>
       </c>
       <c r="S21" t="n">
-        <v>31.4</v>
+        <v>31.5</v>
       </c>
       <c r="T21" t="n">
-        <v>42.4</v>
+        <v>42.6</v>
       </c>
       <c r="U21" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="V21" t="n">
         <v>14.5</v>
@@ -4182,7 +4249,7 @@
         <v>2.4</v>
       </c>
       <c r="Y21" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Z21" t="n">
         <v>20.6</v>
@@ -4191,19 +4258,19 @@
         <v>19.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>106</v>
+        <v>106.1</v>
       </c>
       <c r="AC21" t="n">
-        <v>-2.1</v>
+        <v>-2</v>
       </c>
       <c r="AD21" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AE21" t="n">
         <v>22</v>
       </c>
       <c r="AF21" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AG21" t="n">
         <v>22</v>
@@ -4218,7 +4285,7 @@
         <v>1</v>
       </c>
       <c r="AK21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL21" t="n">
         <v>1</v>
@@ -4227,7 +4294,7 @@
         <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO21" t="n">
         <v>24</v>
@@ -4245,13 +4312,13 @@
         <v>8</v>
       </c>
       <c r="AT21" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AU21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW21" t="n">
         <v>16</v>
@@ -4263,7 +4330,7 @@
         <v>23</v>
       </c>
       <c r="AZ21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA21" t="n">
         <v>29</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-7-2008-09</t>
+          <t>2009-03-07</t>
         </is>
       </c>
     </row>
@@ -4301,58 +4368,58 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E22" t="n">
         <v>16</v>
       </c>
       <c r="F22" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G22" t="n">
-        <v>0.258</v>
+        <v>0.262</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
       </c>
       <c r="I22" t="n">
-        <v>36.8</v>
+        <v>36.9</v>
       </c>
       <c r="J22" t="n">
         <v>81.90000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
       </c>
       <c r="L22" t="n">
         <v>4.2</v>
       </c>
       <c r="M22" t="n">
-        <v>11.7</v>
+        <v>11.5</v>
       </c>
       <c r="N22" t="n">
-        <v>0.362</v>
+        <v>0.366</v>
       </c>
       <c r="O22" t="n">
         <v>20.2</v>
       </c>
       <c r="P22" t="n">
-        <v>25.9</v>
+        <v>26</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.78</v>
+        <v>0.778</v>
       </c>
       <c r="R22" t="n">
         <v>12.4</v>
       </c>
       <c r="S22" t="n">
-        <v>30.7</v>
+        <v>30.8</v>
       </c>
       <c r="T22" t="n">
-        <v>43.1</v>
+        <v>43.2</v>
       </c>
       <c r="U22" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="V22" t="n">
         <v>16.5</v>
@@ -4370,16 +4437,16 @@
         <v>20.7</v>
       </c>
       <c r="AA22" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB22" t="n">
-        <v>98</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AC22" t="n">
-        <v>-5.8</v>
+        <v>-5.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AE22" t="n">
         <v>26</v>
@@ -4397,10 +4464,10 @@
         <v>12</v>
       </c>
       <c r="AJ22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AK22" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL22" t="n">
         <v>29</v>
@@ -4409,13 +4476,13 @@
         <v>30</v>
       </c>
       <c r="AN22" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AO22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AQ22" t="n">
         <v>12</v>
@@ -4430,13 +4497,13 @@
         <v>3</v>
       </c>
       <c r="AU22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV22" t="n">
         <v>30</v>
       </c>
       <c r="AW22" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AX22" t="n">
         <v>22</v>
@@ -4445,10 +4512,10 @@
         <v>18</v>
       </c>
       <c r="AZ22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BB22" t="n">
         <v>20</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-7-2008-09</t>
+          <t>2009-03-07</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>6.9</v>
       </c>
       <c r="AD23" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AE23" t="n">
         <v>4</v>
@@ -4576,13 +4643,13 @@
         <v>23</v>
       </c>
       <c r="AI23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AJ23" t="n">
         <v>25</v>
       </c>
       <c r="AK23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL23" t="n">
         <v>2</v>
@@ -4591,7 +4658,7 @@
         <v>2</v>
       </c>
       <c r="AN23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO23" t="n">
         <v>10</v>
@@ -4618,7 +4685,7 @@
         <v>15</v>
       </c>
       <c r="AW23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX23" t="n">
         <v>10</v>
@@ -4627,7 +4694,7 @@
         <v>2</v>
       </c>
       <c r="AZ23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA23" t="n">
         <v>8</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-7-2008-09</t>
+          <t>2009-03-07</t>
         </is>
       </c>
     </row>
@@ -4665,25 +4732,25 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F24" t="n">
         <v>30</v>
       </c>
       <c r="G24" t="n">
-        <v>0.5</v>
+        <v>0.492</v>
       </c>
       <c r="H24" t="n">
         <v>48.1</v>
       </c>
       <c r="I24" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="J24" t="n">
-        <v>80.3</v>
+        <v>80.2</v>
       </c>
       <c r="K24" t="n">
         <v>0.455</v>
@@ -4695,31 +4762,31 @@
         <v>13.2</v>
       </c>
       <c r="N24" t="n">
-        <v>0.316</v>
+        <v>0.318</v>
       </c>
       <c r="O24" t="n">
         <v>19.5</v>
       </c>
       <c r="P24" t="n">
-        <v>26.2</v>
+        <v>26.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.742</v>
+        <v>0.744</v>
       </c>
       <c r="R24" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="S24" t="n">
-        <v>29.6</v>
+        <v>29.7</v>
       </c>
       <c r="T24" t="n">
-        <v>42.4</v>
+        <v>42.5</v>
       </c>
       <c r="U24" t="n">
         <v>20.4</v>
       </c>
       <c r="V24" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W24" t="n">
         <v>8.1</v>
@@ -4728,19 +4795,19 @@
         <v>5.3</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>96.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AD24" t="n">
         <v>30</v>
@@ -4749,7 +4816,7 @@
         <v>16</v>
       </c>
       <c r="AF24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG24" t="n">
         <v>16</v>
@@ -4764,7 +4831,7 @@
         <v>14</v>
       </c>
       <c r="AK24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL24" t="n">
         <v>30</v>
@@ -4782,7 +4849,7 @@
         <v>7</v>
       </c>
       <c r="AQ24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR24" t="n">
         <v>2</v>
@@ -4791,7 +4858,7 @@
         <v>19</v>
       </c>
       <c r="AT24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AU24" t="n">
         <v>20</v>
@@ -4800,16 +4867,16 @@
         <v>18</v>
       </c>
       <c r="AW24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX24" t="n">
         <v>9</v>
       </c>
       <c r="AY24" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-7-2008-09</t>
+          <t>2009-03-07</t>
         </is>
       </c>
     </row>
@@ -4925,16 +4992,16 @@
         <v>1.6</v>
       </c>
       <c r="AD25" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE25" t="n">
         <v>12</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>13</v>
       </c>
       <c r="AF25" t="n">
         <v>12</v>
       </c>
       <c r="AG25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH25" t="n">
         <v>24</v>
@@ -4949,7 +5016,7 @@
         <v>1</v>
       </c>
       <c r="AL25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM25" t="n">
         <v>19</v>
@@ -4964,7 +5031,7 @@
         <v>5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR25" t="n">
         <v>24</v>
@@ -4982,7 +5049,7 @@
         <v>29</v>
       </c>
       <c r="AW25" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AX25" t="n">
         <v>12</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-7-2008-09</t>
+          <t>2009-03-07</t>
         </is>
       </c>
     </row>
@@ -5032,46 +5099,46 @@
         <v>61</v>
       </c>
       <c r="E26" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G26" t="n">
-        <v>0.639</v>
+        <v>0.623</v>
       </c>
       <c r="H26" t="n">
         <v>48.3</v>
       </c>
       <c r="I26" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="J26" t="n">
-        <v>79.09999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="K26" t="n">
-        <v>0.464</v>
+        <v>0.462</v>
       </c>
       <c r="L26" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="M26" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="N26" t="n">
-        <v>0.378</v>
+        <v>0.38</v>
       </c>
       <c r="O26" t="n">
-        <v>18.7</v>
+        <v>18.5</v>
       </c>
       <c r="P26" t="n">
-        <v>24.5</v>
+        <v>24.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.764</v>
+        <v>0.76</v>
       </c>
       <c r="R26" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="S26" t="n">
         <v>28.2</v>
@@ -5080,49 +5147,49 @@
         <v>41.1</v>
       </c>
       <c r="U26" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="V26" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="W26" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="X26" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y26" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>99</v>
+      </c>
+      <c r="AC26" t="n">
         <v>3.8</v>
       </c>
-      <c r="Z26" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>99.3</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AD26" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AE26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG26" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AH26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ26" t="n">
         <v>21</v>
@@ -5134,19 +5201,19 @@
         <v>10</v>
       </c>
       <c r="AM26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AN26" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AO26" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AP26" t="n">
         <v>18</v>
       </c>
       <c r="AQ26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR26" t="n">
         <v>1</v>
@@ -5155,7 +5222,7 @@
         <v>29</v>
       </c>
       <c r="AT26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU26" t="n">
         <v>21</v>
@@ -5167,7 +5234,7 @@
         <v>26</v>
       </c>
       <c r="AX26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY26" t="n">
         <v>3</v>
@@ -5179,10 +5246,10 @@
         <v>13</v>
       </c>
       <c r="BB26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC26" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-7-2008-09</t>
+          <t>2009-03-07</t>
         </is>
       </c>
     </row>
@@ -5289,13 +5356,13 @@
         <v>-9.199999999999999</v>
       </c>
       <c r="AD27" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AE27" t="n">
         <v>30</v>
       </c>
       <c r="AF27" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AG27" t="n">
         <v>30</v>
@@ -5304,22 +5371,22 @@
         <v>3</v>
       </c>
       <c r="AI27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ27" t="n">
         <v>13</v>
       </c>
       <c r="AK27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AM27" t="n">
         <v>14</v>
       </c>
       <c r="AN27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO27" t="n">
         <v>5</v>
@@ -5334,7 +5401,7 @@
         <v>27</v>
       </c>
       <c r="AS27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT27" t="n">
         <v>30</v>
@@ -5346,13 +5413,13 @@
         <v>28</v>
       </c>
       <c r="AW27" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX27" t="n">
         <v>26</v>
       </c>
       <c r="AY27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ27" t="n">
         <v>28</v>
@@ -5361,7 +5428,7 @@
         <v>11</v>
       </c>
       <c r="BB27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC27" t="n">
         <v>30</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-7-2008-09</t>
+          <t>2009-03-07</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>4</v>
       </c>
       <c r="AD28" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AE28" t="n">
         <v>5</v>
@@ -5501,7 +5568,7 @@
         <v>8</v>
       </c>
       <c r="AN28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AO28" t="n">
         <v>30</v>
@@ -5510,7 +5577,7 @@
         <v>30</v>
       </c>
       <c r="AQ28" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AR28" t="n">
         <v>30</v>
@@ -5546,7 +5613,7 @@
         <v>23</v>
       </c>
       <c r="BC28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-7-2008-09</t>
+          <t>2009-03-07</t>
         </is>
       </c>
     </row>
@@ -5674,19 +5741,19 @@
         <v>19</v>
       </c>
       <c r="AK29" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AL29" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AM29" t="n">
         <v>22</v>
       </c>
       <c r="AN29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP29" t="n">
         <v>27</v>
@@ -5707,7 +5774,7 @@
         <v>8</v>
       </c>
       <c r="AV29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW29" t="n">
         <v>29</v>
@@ -5716,7 +5783,7 @@
         <v>13</v>
       </c>
       <c r="AY29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ29" t="n">
         <v>4</v>
@@ -5725,10 +5792,10 @@
         <v>23</v>
       </c>
       <c r="BB29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-7-2008-09</t>
+          <t>2009-03-07</t>
         </is>
       </c>
     </row>
@@ -5835,19 +5902,19 @@
         <v>3.9</v>
       </c>
       <c r="AD30" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AE30" t="n">
         <v>8</v>
       </c>
       <c r="AF30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI30" t="n">
         <v>6</v>
@@ -5859,13 +5926,13 @@
         <v>3</v>
       </c>
       <c r="AL30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM30" t="n">
         <v>26</v>
       </c>
       <c r="AN30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO30" t="n">
         <v>3</v>
@@ -5874,7 +5941,7 @@
         <v>3</v>
       </c>
       <c r="AQ30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR30" t="n">
         <v>9</v>
@@ -5898,7 +5965,7 @@
         <v>16</v>
       </c>
       <c r="AY30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ30" t="n">
         <v>24</v>
@@ -5910,7 +5977,7 @@
         <v>6</v>
       </c>
       <c r="BC30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-7-2008-09</t>
+          <t>2009-03-07</t>
         </is>
       </c>
     </row>
@@ -5939,61 +6006,61 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E31" t="n">
         <v>14</v>
       </c>
       <c r="F31" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G31" t="n">
-        <v>0.222</v>
+        <v>0.226</v>
       </c>
       <c r="H31" t="n">
         <v>48.1</v>
       </c>
       <c r="I31" t="n">
-        <v>36.1</v>
+        <v>36</v>
       </c>
       <c r="J31" t="n">
-        <v>80.90000000000001</v>
+        <v>81</v>
       </c>
       <c r="K31" t="n">
-        <v>0.446</v>
+        <v>0.445</v>
       </c>
       <c r="L31" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="M31" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="N31" t="n">
-        <v>0.325</v>
+        <v>0.321</v>
       </c>
       <c r="O31" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="P31" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.763</v>
+        <v>0.762</v>
       </c>
       <c r="R31" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="S31" t="n">
-        <v>27.9</v>
+        <v>28</v>
       </c>
       <c r="T31" t="n">
-        <v>39.6</v>
+        <v>39.7</v>
       </c>
       <c r="U31" t="n">
         <v>20.1</v>
       </c>
       <c r="V31" t="n">
-        <v>14.2</v>
+        <v>14</v>
       </c>
       <c r="W31" t="n">
         <v>7.4</v>
@@ -6011,13 +6078,13 @@
         <v>19.5</v>
       </c>
       <c r="AB31" t="n">
-        <v>94.40000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="AC31" t="n">
-        <v>-7.8</v>
+        <v>-7.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
@@ -6038,7 +6105,7 @@
         <v>12</v>
       </c>
       <c r="AK31" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AL31" t="n">
         <v>25</v>
@@ -6053,10 +6120,10 @@
         <v>26</v>
       </c>
       <c r="AP31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AQ31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR31" t="n">
         <v>8</v>
@@ -6065,7 +6132,7 @@
         <v>30</v>
       </c>
       <c r="AT31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU31" t="n">
         <v>24</v>
@@ -6074,7 +6141,7 @@
         <v>12</v>
       </c>
       <c r="AW31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX31" t="n">
         <v>25</v>
@@ -6083,10 +6150,10 @@
         <v>21</v>
       </c>
       <c r="AZ31" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA31" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB31" t="n">
         <v>27</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-7-2008-09</t>
+          <t>2009-03-07</t>
         </is>
       </c>
     </row>
